--- a/Praktek Komputer - Spreadsheet/01- Fungsi Dasar Teks/01- Fungsi Dasar Teks.xlsx
+++ b/Praktek Komputer - Spreadsheet/01- Fungsi Dasar Teks/01- Fungsi Dasar Teks.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yamin Folder\Praktek Komputer\Bahan Praktek\48 Rumus Excell\01- Fungsi Dasar Teks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AY Labs\UIN Bukittinggi\Praktek Komputer\Prakom - Belajar Rumus Excell\01- Fungsi Dasar Teks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AC06AA-5D3E-4015-AD4D-66825B7176A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5183B3FD-6AFE-423C-962D-DB87C56D2C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="866" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -238,14 +238,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -308,8 +300,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,6 +325,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF009900"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,32 +398,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -426,6 +432,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF009900"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -746,12 +757,12 @@
       <c r="B1" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -762,7 +773,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -773,7 +784,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -784,7 +795,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -795,7 +806,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
+      <c r="A6" s="12">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -806,7 +817,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18">
+      <c r="A7" s="12">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -817,7 +828,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
+      <c r="A8" s="12">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -828,7 +839,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="18">
+      <c r="A9" s="12">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -839,7 +850,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18">
+      <c r="A10" s="12">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -850,7 +861,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="18">
+      <c r="A11" s="12">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -861,7 +872,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18">
+      <c r="A12" s="12">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -872,7 +883,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18">
+      <c r="A13" s="12">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -883,7 +894,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18">
+      <c r="A14" s="12">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -894,7 +905,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18">
+      <c r="A15" s="12">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -905,7 +916,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="18">
+      <c r="A16" s="12">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -976,8 +987,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1028,8 +1039,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="16"/>
-      <c r="D5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1080,8 +1091,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1132,8 +1143,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1195,8 +1206,8 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C7" s="14"/>
-      <c r="D7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1263,8 +1274,8 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C7" s="14"/>
-      <c r="D7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1327,11 +1338,8 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C7" s="14" t="b">
-        <f>EXACT(D3,D4)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1382,11 +1390,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="14" t="str">
-        <f>UPPER(D3)</f>
-        <v>SAYA LAGI BELAJAR</v>
-      </c>
-      <c r="D5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1438,8 +1443,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1494,8 +1499,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1546,8 +1551,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1598,8 +1603,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1650,8 +1655,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1702,8 +1707,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1754,8 +1759,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
